--- a/backend/app/assets/importTopicTemplate.xlsx
+++ b/backend/app/assets/importTopicTemplate.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srr17\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B98AF0-776D-43A2-BF8C-259DA4608F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,107 +27,474 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
-  <si>
-    <t>一级知识点</t>
-  </si>
-  <si>
-    <t>二级知识点</t>
-  </si>
-  <si>
-    <t>三级知识点</t>
-  </si>
-  <si>
-    <t>四级知识点</t>
-  </si>
-  <si>
-    <t>五级知识点</t>
-  </si>
-  <si>
-    <t>六级知识点</t>
-  </si>
-  <si>
-    <t>七级知识点</t>
-  </si>
-  <si>
-    <t>前置知识点</t>
-  </si>
-  <si>
-    <t>后置知识点</t>
-  </si>
-  <si>
-    <t>关联知识点</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+  <si>
+    <r>
+      <t>1. 后面带“*”的为必填项
+2. 节点类型：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分类</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>知识点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. A列仅支持填写一个节点类型，B列至H列每行仅支持填写一个节点，I列至K列填写对应节点的前置、后置和关联节点，多个节点之间用英文分号";"隔开
+4. 任意两个节点之间仅支持存在一种关系（前置、后置或关联），</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>新导入的关系将覆盖旧关系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. 固定标签包括：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>重点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>难点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>考点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>课程思政</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，可根据需要</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>自定义标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，多个标签之间用英文分号";"隔开
+6. 知识点分类包括：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>事实性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>概念性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>程序性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>元认知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，每个知识点只能填入一个知识点分类，分类</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>支持填写知识点分类
+7. 节点说明仅支持输入文本，暂不支持图片、公式等
+8. 单个分类或知识点长度最长</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>256</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>字符，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>知识点后不可填写子级节点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。
+9.图谱和导入模板中知识点总和最多</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个，关系最多</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>条，标签最多</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>个。
+10. 请不要删除此行，也不要删除模板中的任何列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>节点类型</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>节点名称</t>
+  </si>
+  <si>
+    <t>前置节点</t>
+  </si>
+  <si>
+    <t>后置节点</t>
+  </si>
+  <si>
+    <t>关联节点</t>
   </si>
   <si>
     <t>标签</t>
   </si>
   <si>
-    <t>认知维度</t>
+    <t>知识点分类</t>
+  </si>
+  <si>
+    <t>节点说明</t>
   </si>
   <si>
     <t>分类</t>
   </si>
   <si>
-    <t>教学目标</t>
-  </si>
-  <si>
-    <t>知识点说明</t>
-  </si>
-  <si>
-    <t>标签名1</t>
-  </si>
-  <si>
-    <t>标签名1.1</t>
-  </si>
-  <si>
-    <t>标签名1.1.1</t>
-  </si>
-  <si>
-    <t>标签名1.1.2</t>
-  </si>
-  <si>
-    <t>标签名1.1.3;标签名1.2.1</t>
-  </si>
-  <si>
-    <t>标签名2</t>
+    <t>分类1</t>
+  </si>
+  <si>
+    <t>分类1.1</t>
+  </si>
+  <si>
+    <t>分类1.1.1</t>
+  </si>
+  <si>
+    <t>知识点</t>
+  </si>
+  <si>
+    <t>知识点1.1.2</t>
+  </si>
+  <si>
+    <t>知识点1.2;知识点1.3</t>
   </si>
   <si>
     <t>考点;难点</t>
   </si>
   <si>
-    <t>记忆</t>
-  </si>
-  <si>
     <t>事实性</t>
   </si>
   <si>
-    <t>标签名1.1.3</t>
-  </si>
-  <si>
-    <t>标签名1.2</t>
-  </si>
-  <si>
-    <t>标签名1.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使用说明：
-1. A列至G列对应知识点的层级关系，区间内每行只能填写一个知识点
-2. H列至J列填写对应知识点的前置、后置和关联知识点，多个知识点之间用英文分号";"隔开
-3. 任意两个知识点之间只能存在一种关系（前置、后置或关联），新导入的关系将覆盖旧关系，关系设置总数上限为2000个
-4. 固定标签包括：重点、难点、考点、课程思政，可根据需要自定义标签，多个标签之间用英文分号";"隔开
-5. 认知维度包括：记忆、理解、应用、分析、评价、创造，每个知识点只能填入一个认知维度
-6. 知识点分类包括：事实性、概念性、程序性、元认知，每个知识点只能填入一个分类
-7. 知识点说明仅支持输入文本，暂不支持图片、公式等
-8. 请不要删除此行，也不要删除模板中的任何列
-</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>知识点1.2</t>
+  </si>
+  <si>
+    <t>知识点1.3</t>
+  </si>
+  <si>
+    <t>分类2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,44 +504,180 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFC00000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,8 +690,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -201,15 +886,98 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.149937437055574"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -217,60 +985,233 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14993743705557422"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="8" tint="0.79992065187536243"/>
+          <bgColor theme="8" tint="0.799920651875362"/>
         </patternFill>
       </fill>
     </dxf>
@@ -293,7 +1234,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="表样式 1" pivot="0" count="3" xr9:uid="{DB8925D1-9B97-444F-8556-FD19ED651519}">
+    <tableStyle name="表样式 1" pivot="0" count="3" xr9:uid="{0F8AB17E-CD9F-4BFF-B778-4656EC7D1B22}">
       <tableStyleElement type="wholeTable" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
@@ -301,15 +1242,12 @@
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="FF3A8BFF"/>
+      <color rgb="003A8BFF"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -567,144 +1505,156 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="7" width="11" customWidth="1"/>
-    <col min="8" max="15" width="15.59765625" customWidth="1"/>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+    <col min="2" max="8" width="11" customWidth="1"/>
+    <col min="9" max="14" width="15.6296296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+    <row r="1" ht="158.1" customHeight="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="3"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="D6" t="s">
         <v>14</v>
       </c>
+      <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>15</v>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>16</v>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>